--- a/input.xlsx
+++ b/input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1352" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABBA670F-8EBD-46A0-88D7-23996C8CEBB2}"/>
+  <xr:revisionPtr revIDLastSave="1365" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA551C85-FA08-408F-B843-E797C6AF88DC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="408">
   <si>
     <t>Taxes</t>
   </si>
@@ -1268,6 +1268,15 @@
   </si>
   <si>
     <t>Prix TTC de l'unité</t>
+  </si>
+  <si>
+    <t>Contrat d'entretien de la chaudière à gaz, bois et granules Dalkia</t>
+  </si>
+  <si>
+    <t>Dalkia</t>
+  </si>
+  <si>
+    <t>Contrat P2, engagement sur 3 ans, a priori pas de livraison</t>
   </si>
 </sst>
 </file>
@@ -1367,16 +1376,7 @@
   </cellStyles>
   <dxfs count="31">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1395,16 +1395,61 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1700,7 +1745,16 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -1719,61 +1773,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1799,8 +1808,8 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Monétaire"/>
-    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="22" totalsRowDxfId="21" dataCellStyle="Monétaire"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1813,47 +1822,47 @@
     <sortCondition ref="A1:A180"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="19"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="21">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="18">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="13"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="12"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="10"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I37" totalsRowShown="0">
-  <autoFilter ref="A1:I37" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I38" totalsRowShown="0">
+  <autoFilter ref="A1:I38" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H37">
     <sortCondition ref="B1:B37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="25">
       <calculatedColumnFormula>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1880,13 +1889,13 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix TTC de l'unité" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix TTC de l'unité" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
-    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (kW)" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (kW)" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{D0B5F61C-1D85-4C5E-A117-B774F88FE50E}" name="Seuil de durée d'activation (mn)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6880,7 +6889,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" customWidth="1"/>
@@ -7873,6 +7882,33 @@
       </c>
       <c r="I37" s="2" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" t="s">
+        <v>406</v>
+      </c>
+      <c r="E38" s="4">
+        <v>10932.1</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>13118.52</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1365" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA551C85-FA08-408F-B843-E797C6AF88DC}"/>
+  <xr:revisionPtr revIDLastSave="1366" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75ADD3F5-8AE0-40BD-9CA2-45A4CD25B930}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="408">
   <si>
     <t>Taxes</t>
   </si>
@@ -7910,6 +7910,9 @@
       <c r="H38" s="2" t="s">
         <v>407</v>
       </c>
+      <c r="I38" t="s">
+        <v>188</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1366" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75ADD3F5-8AE0-40BD-9CA2-45A4CD25B930}"/>
+  <xr:revisionPtr revIDLastSave="1367" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F4AC2A7-AD15-4D68-8B7A-52210FB393DD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -8052,8 +8052,8 @@
         <v>397</v>
       </c>
       <c r="E2" s="1">
-        <f>392*1.2</f>
-        <v>470.4</v>
+        <f>310*1.2</f>
+        <v>372</v>
       </c>
       <c r="F2" s="12">
         <v>4900</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1367" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F4AC2A7-AD15-4D68-8B7A-52210FB393DD}"/>
+  <xr:revisionPtr revIDLastSave="1419" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE078EAE-918E-4E5C-9DF0-DB525F631E88}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="417">
   <si>
     <t>Taxes</t>
   </si>
@@ -1277,6 +1277,42 @@
   </si>
   <si>
     <t>Contrat P2, engagement sur 3 ans, a priori pas de livraison</t>
+  </si>
+  <si>
+    <t>Consommation de sel pour adoucir l'eau - Estimation basse</t>
+  </si>
+  <si>
+    <t>Esimation IA</t>
+  </si>
+  <si>
+    <t>L’adoucisseur est récent et volumétrique : il se régénère selon le volume d’eau réellement consommé, et non selon un calendrier fixe.
+La régénération se fait à contre-courant, ce qui économise du sel.
+Le réglage est bien ajusté, avec un mitigeur de dureté qui laisse passer une partie d’eau brute.
+Il consomme 25 g de sel par °f·m³, soit 0,8 t par an.
+Le sel est acheté au prix du détail le plus bas, 0,40 €/kg (pastilles en sac de 25 kg), ce qui donne environ 320 €.</t>
+  </si>
+  <si>
+    <t>L’appareil est fonctionnel mais pas optimisé : réglage standard du fabricant, régénération moins économe.
+Il consomme 40 g par °f·m³, soit 1,3 t par an.
+Le sel coûte 0,50 €/kg, par exemple en achat groupé ou livré, ce qui donne environ 640 €.
+C’est ce que je considère comme le cas le plus probable pour une résidence sans suivi particulier.</t>
+  </si>
+  <si>
+    <t>L’appareil est ancien, régénéré au chronomètre, c’est-à-dire à intervalles fixes même si l’eau n’a pas été consommée, ou surdimensionné. Il peut aussi être réglé pour descendre trop bas en dureté.
+Il consomme 80 g par °f·m³, soit 2,6 t par an.
+Le sel coûte 0,70 €/kg, avec livraison et petites quantités, ce qui donne environ 1 800 €.</t>
+  </si>
+  <si>
+    <t>Maintenance de la VMC</t>
+  </si>
+  <si>
+    <t>Consommation de sel pour adoucir l'eau</t>
+  </si>
+  <si>
+    <t>Inclus dans le contrat P2 de Dalkia (pas de prix exact)</t>
+  </si>
+  <si>
+    <t>Maintenance de la VMC Dalkia</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1359,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1342,13 +1378,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1368,6 +1413,9 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
@@ -1846,8 +1894,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I38" totalsRowShown="0">
-  <autoFilter ref="A1:I38" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I42" totalsRowShown="0">
+  <autoFilter ref="A1:I42" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H37">
     <sortCondition ref="B1:B37"/>
   </sortState>
@@ -6889,17 +6937,17 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="66.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="124.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="132.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7913,6 +7961,128 @@
       <c r="I38" t="s">
         <v>188</v>
       </c>
+    </row>
+    <row r="39" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" t="s">
+        <v>409</v>
+      </c>
+      <c r="E39" s="4">
+        <v>320</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>320</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" t="s">
+        <v>409</v>
+      </c>
+      <c r="E40" s="4">
+        <v>640</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="13">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>640</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="s">
+        <v>409</v>
+      </c>
+      <c r="E41" s="14">
+        <v>1800</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="15">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>1800</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>413</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>406</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="15">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="I42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="C43"/>
+      <c r="G43" s="13"/>
+      <c r="I43" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7926,7 +8096,7 @@
           <x14:formula1>
             <xm:f>Provisions!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>C1:C1048576</xm:sqref>
+          <xm:sqref>C45:C1048576 C1:C43</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1419" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE078EAE-918E-4E5C-9DF0-DB525F631E88}"/>
+  <xr:revisionPtr revIDLastSave="1421" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5433CA94-0E5A-44AE-8A12-0AC1B99ADD97}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="419">
   <si>
     <t>Taxes</t>
   </si>
@@ -1313,6 +1313,12 @@
   </si>
   <si>
     <t>Maintenance de la VMC Dalkia</t>
+  </si>
+  <si>
+    <t>Consommation de sel pour adoucir l'eau - Estimation moyenne</t>
+  </si>
+  <si>
+    <t>Consommation de sel pour adoucir l'eau - Estimation haute</t>
   </si>
 </sst>
 </file>
@@ -7995,7 +8001,7 @@
         <v>414</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C40" t="s">
         <v>72</v>
@@ -8025,7 +8031,7 @@
         <v>414</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>72</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1421" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5433CA94-0E5A-44AE-8A12-0AC1B99ADD97}"/>
+  <xr:revisionPtr revIDLastSave="1460" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC9F63A-3951-4103-A618-B682D747DAB0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="428">
   <si>
     <t>Taxes</t>
   </si>
@@ -423,13 +423,7 @@
     <t>Contrat d'entretien de la chaudière à gaz, bois et granules CRAM</t>
   </si>
   <si>
-    <t>Contrat d'entretien de la chaudière à gaz, bois et granules PROCHALOR</t>
-  </si>
-  <si>
     <t>Contrat d'entretien de la chaudière à gaz, bois et granules D&amp;T</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Contrat d'entretien classique 6j/7 interventions de 8h00 à 18h00 avec engagement sur 1 an, ne couvre que les 2 visites réglementaires+réparations pour usure normale. Interdit de les filmer et pas de recours pour violation de domicile possible</t>
   </si>
   <si>
     <t xml:space="preserve"> Contrat d'entretien classique 6j/7 interventions de 8h00 à 18h00 avec engagement sur 2 ans, ne couvre que les 2 visites réglementaires+réparations pour usure normale. Interdit de les filmer et pas de recours pour violation de domicile possible</t>
@@ -1276,9 +1270,6 @@
     <t>Dalkia</t>
   </si>
   <si>
-    <t>Contrat P2, engagement sur 3 ans, a priori pas de livraison</t>
-  </si>
-  <si>
     <t>Consommation de sel pour adoucir l'eau - Estimation basse</t>
   </si>
   <si>
@@ -1319,6 +1310,42 @@
   </si>
   <si>
     <t>Consommation de sel pour adoucir l'eau - Estimation haute</t>
+  </si>
+  <si>
+    <t>Contrat d'entretien de la chaudière à gaz, bois et granules Engie Solution</t>
+  </si>
+  <si>
+    <t>Ont répondu trop tard à la demande d'informations, mais gros groupe qui a une expertise de la biomasse (pas de devis)</t>
+  </si>
+  <si>
+    <t>Contrat d'entretien de la chaudière à gaz, bois et granules PROCHALOR Pack confort</t>
+  </si>
+  <si>
+    <t>Contrat d'entretien de la chaudière à gaz, bois et granules PROCHALOR Pack sérénité</t>
+  </si>
+  <si>
+    <t>Contrat d'entretien de la chaudière à gaz, bois et granules SCEM</t>
+  </si>
+  <si>
+    <t>SCEM</t>
+  </si>
+  <si>
+    <t>Petite structure, interventions de dépannage sur devis (pas de barême de prix). VMC non incluse. 403,63 €HT la tonne de granulé</t>
+  </si>
+  <si>
+    <t>Petite structure, interventions de dépannage sur devis (pas de barême de prix). VMC incluse + produits d'entretien de la chaudière, 403,63 €HT la tonne de granulé</t>
+  </si>
+  <si>
+    <t>Petite structure, interventions de dépannage hors forfait selon barême de prix. VMC non incluse. 392 € HT la tonne de granulé</t>
+  </si>
+  <si>
+    <t>Engie Solutions</t>
+  </si>
+  <si>
+    <t>Contrat P2, engagement sur 3 ans, a priori pas de livraison. Contrôle du silo et commande faites bénévolement. Recommandé par le revendeur de la chaudière biomasse SB Thermique pour leur expertise. Pas de gestion de l'approvisionnement. Prix de Gruchy (fournisseur indépendant contacté par le conseil syndical) : 310€ HT par tonne de granulé</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contrat d'entretien classique 6j/7 interventions de 8h00 à 18h00 avec engagement sur 1 an, ne couvre que les 2 visites réglementaires+réparations pour usure normale. Interdit de les filmer et pas de recours pour violation de domicile possible. Sélectionné pour 1 an avant passage chez Eurosofia. Tel depannage : 01 34 78 55 40 /depannage@fermatic.fr</t>
   </si>
 </sst>
 </file>
@@ -1900,10 +1927,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I42" totalsRowShown="0">
-  <autoFilter ref="A1:I42" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H37">
-    <sortCondition ref="B1:B37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I45" totalsRowShown="0">
+  <autoFilter ref="A1:I45" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I45">
+    <sortCondition ref="C1:C45"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="30"/>
@@ -2235,13 +2262,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D1" t="s">
         <v>94</v>
@@ -2250,15 +2277,15 @@
         <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
@@ -2270,18 +2297,18 @@
         <v>35000</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>46</v>
@@ -2290,18 +2317,18 @@
         <v>27000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -2313,7 +2340,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -2331,7 +2358,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
@@ -2349,7 +2376,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -2367,7 +2394,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -2385,7 +2412,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
@@ -2403,7 +2430,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
         <v>64</v>
@@ -2421,13 +2448,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s">
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" t="s">
         <v>83</v>
@@ -2439,13 +2466,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s">
         <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
         <v>82</v>
@@ -2457,13 +2484,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
         <v>81</v>
@@ -2475,13 +2502,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
         <v>84</v>
@@ -2493,27 +2520,27 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E15" s="1">
         <v>2000</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s">
         <v>54</v>
@@ -2531,7 +2558,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s">
         <v>89</v>
@@ -2549,7 +2576,7 @@
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s">
         <v>62</v>
@@ -2564,52 +2591,52 @@
         <v>1050</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E19" s="1">
         <v>1000</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E20" s="1">
         <v>1000</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s">
         <v>60</v>
@@ -2624,12 +2651,12 @@
         <v>920</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s">
         <v>61</v>
@@ -2644,12 +2671,12 @@
         <v>900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s">
         <v>69</v>
@@ -2667,7 +2694,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s">
         <v>66</v>
@@ -2682,12 +2709,12 @@
         <v>750</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
         <v>56</v>
@@ -2705,7 +2732,7 @@
     </row>
     <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
         <v>63</v>
@@ -2720,12 +2747,12 @@
         <v>580</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B27" t="s">
         <v>68</v>
@@ -2743,7 +2770,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B28" t="s">
         <v>73</v>
@@ -2758,12 +2785,12 @@
         <v>450</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B29" t="s">
         <v>76</v>
@@ -2778,12 +2805,12 @@
         <v>360</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
         <v>75</v>
@@ -2798,12 +2825,12 @@
         <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
         <v>58</v>
@@ -2818,12 +2845,12 @@
         <v>240</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B32" t="s">
         <v>57</v>
@@ -2841,7 +2868,7 @@
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s">
         <v>74</v>
@@ -2856,12 +2883,12 @@
         <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B34" t="s">
         <v>59</v>
@@ -2879,22 +2906,22 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D35" t="s">
         <v>209</v>
-      </c>
-      <c r="D35" t="s">
-        <v>211</v>
       </c>
       <c r="E35" s="1">
         <v>0</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2931,49 +2958,49 @@
         <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>156</v>
-      </c>
       <c r="P1" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -2981,7 +3008,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C2">
         <v>462</v>
@@ -2995,7 +3022,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C3">
         <v>119</v>
@@ -3021,7 +3048,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C4">
         <v>83</v>
@@ -3047,7 +3074,7 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C5">
         <v>130</v>
@@ -3073,7 +3100,7 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -3099,7 +3126,7 @@
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C7">
         <v>122</v>
@@ -3125,7 +3152,7 @@
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C8">
         <v>55</v>
@@ -3151,7 +3178,7 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C9">
         <v>96</v>
@@ -3177,7 +3204,7 @@
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3203,7 +3230,7 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C11">
         <v>129</v>
@@ -3229,7 +3256,7 @@
         <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C12">
         <v>58</v>
@@ -3255,7 +3282,7 @@
         <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C13">
         <v>91</v>
@@ -3281,7 +3308,7 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C14" s="8">
         <v>86</v>
@@ -3315,7 +3342,7 @@
         <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C15">
         <v>94</v>
@@ -3341,7 +3368,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -3367,7 +3394,7 @@
         <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C17">
         <v>162</v>
@@ -3393,7 +3420,7 @@
         <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C18">
         <v>202</v>
@@ -3419,7 +3446,7 @@
         <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C19">
         <v>294</v>
@@ -3445,7 +3472,7 @@
         <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C20">
         <v>81</v>
@@ -3471,7 +3498,7 @@
         <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C21">
         <v>115</v>
@@ -3497,7 +3524,7 @@
         <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C22">
         <v>112</v>
@@ -3523,7 +3550,7 @@
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C23">
         <v>83</v>
@@ -3549,7 +3576,7 @@
         <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C24">
         <v>118</v>
@@ -3575,7 +3602,7 @@
         <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C25">
         <v>117</v>
@@ -3601,7 +3628,7 @@
         <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C26">
         <v>87</v>
@@ -3627,7 +3654,7 @@
         <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C27">
         <v>125</v>
@@ -3653,7 +3680,7 @@
         <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C28">
         <v>123</v>
@@ -3679,7 +3706,7 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C29">
         <v>88</v>
@@ -3705,7 +3732,7 @@
         <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C30">
         <v>127</v>
@@ -3731,7 +3758,7 @@
         <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C31">
         <v>127</v>
@@ -3757,7 +3784,7 @@
         <v>132</v>
       </c>
       <c r="B32" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C32">
         <v>172</v>
@@ -3783,7 +3810,7 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C33">
         <v>218</v>
@@ -3809,7 +3836,7 @@
         <v>134</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C34">
         <v>102</v>
@@ -3835,7 +3862,7 @@
         <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C35">
         <v>83</v>
@@ -3861,7 +3888,7 @@
         <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C36">
         <v>401</v>
@@ -3875,7 +3902,7 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C37">
         <v>114</v>
@@ -3901,7 +3928,7 @@
         <v>203</v>
       </c>
       <c r="B38" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C38">
         <v>84</v>
@@ -3927,7 +3954,7 @@
         <v>204</v>
       </c>
       <c r="B39" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C39">
         <v>81</v>
@@ -3953,7 +3980,7 @@
         <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C40">
         <v>118</v>
@@ -3979,7 +4006,7 @@
         <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C41">
         <v>120</v>
@@ -4005,7 +4032,7 @@
         <v>207</v>
       </c>
       <c r="B42" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C42">
         <v>89</v>
@@ -4031,7 +4058,7 @@
         <v>208</v>
       </c>
       <c r="B43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C43">
         <v>84</v>
@@ -4057,7 +4084,7 @@
         <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C44">
         <v>124</v>
@@ -4083,7 +4110,7 @@
         <v>210</v>
       </c>
       <c r="B45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C45">
         <v>126</v>
@@ -4109,7 +4136,7 @@
         <v>211</v>
       </c>
       <c r="B46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C46">
         <v>91</v>
@@ -4135,7 +4162,7 @@
         <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C47">
         <v>88</v>
@@ -4161,7 +4188,7 @@
         <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C48">
         <v>131</v>
@@ -4187,7 +4214,7 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -4213,7 +4240,7 @@
         <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C50">
         <v>93</v>
@@ -4239,7 +4266,7 @@
         <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C51">
         <v>59</v>
@@ -4265,7 +4292,7 @@
         <v>217</v>
       </c>
       <c r="B52" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C52">
         <v>166</v>
@@ -4291,7 +4318,7 @@
         <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C53">
         <v>186</v>
@@ -4317,7 +4344,7 @@
         <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C54">
         <v>61</v>
@@ -4343,7 +4370,7 @@
         <v>220</v>
       </c>
       <c r="B55" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C55">
         <v>171</v>
@@ -4369,7 +4396,7 @@
         <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C56">
         <v>178</v>
@@ -4395,7 +4422,7 @@
         <v>222</v>
       </c>
       <c r="B57" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C57">
         <v>62</v>
@@ -4421,7 +4448,7 @@
         <v>223</v>
       </c>
       <c r="B58" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C58">
         <v>174</v>
@@ -4447,7 +4474,7 @@
         <v>224</v>
       </c>
       <c r="B59" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C59">
         <v>181</v>
@@ -4473,7 +4500,7 @@
         <v>225</v>
       </c>
       <c r="B60" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C60" s="8">
         <v>197</v>
@@ -4507,7 +4534,7 @@
         <v>301</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C61">
         <v>169</v>
@@ -4527,7 +4554,7 @@
         <v>302</v>
       </c>
       <c r="B62" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C62">
         <v>158</v>
@@ -4547,7 +4574,7 @@
         <v>303</v>
       </c>
       <c r="B63" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C63">
         <v>71</v>
@@ -4567,7 +4594,7 @@
         <v>305</v>
       </c>
       <c r="B64" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C64">
         <v>134</v>
@@ -4590,7 +4617,7 @@
         <v>306</v>
       </c>
       <c r="B65" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C65">
         <v>147</v>
@@ -4613,7 +4640,7 @@
         <v>307</v>
       </c>
       <c r="B66" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C66">
         <v>155</v>
@@ -4636,7 +4663,7 @@
         <v>308</v>
       </c>
       <c r="B67" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C67" s="8">
         <v>75</v>
@@ -4668,7 +4695,7 @@
         <v>310</v>
       </c>
       <c r="B68" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C68">
         <v>52</v>
@@ -4691,7 +4718,7 @@
         <v>311</v>
       </c>
       <c r="B69" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C69">
         <v>193</v>
@@ -4714,7 +4741,7 @@
         <v>312</v>
       </c>
       <c r="B70" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C70">
         <v>133</v>
@@ -4737,7 +4764,7 @@
         <v>313</v>
       </c>
       <c r="B71" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C71">
         <v>72</v>
@@ -4757,7 +4784,7 @@
         <v>314</v>
       </c>
       <c r="B72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C72">
         <v>79</v>
@@ -4777,7 +4804,7 @@
         <v>315</v>
       </c>
       <c r="B73" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C73">
         <v>85</v>
@@ -4800,7 +4827,7 @@
         <v>316</v>
       </c>
       <c r="B74" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C74">
         <v>90</v>
@@ -4823,7 +4850,7 @@
         <v>401</v>
       </c>
       <c r="B75" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C75">
         <v>7</v>
@@ -4843,7 +4870,7 @@
         <v>402</v>
       </c>
       <c r="B76" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -4863,7 +4890,7 @@
         <v>403</v>
       </c>
       <c r="B77" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C77">
         <v>7</v>
@@ -4883,7 +4910,7 @@
         <v>404</v>
       </c>
       <c r="B78" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C78">
         <v>7</v>
@@ -4903,7 +4930,7 @@
         <v>405</v>
       </c>
       <c r="B79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C79">
         <v>7</v>
@@ -4923,7 +4950,7 @@
         <v>406</v>
       </c>
       <c r="B80" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C80">
         <v>7</v>
@@ -4943,7 +4970,7 @@
         <v>407</v>
       </c>
       <c r="B81" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C81">
         <v>7</v>
@@ -4963,7 +4990,7 @@
         <v>408</v>
       </c>
       <c r="B82" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C82">
         <v>7</v>
@@ -4983,7 +5010,7 @@
         <v>409</v>
       </c>
       <c r="B83" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -5003,7 +5030,7 @@
         <v>410</v>
       </c>
       <c r="B84" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C84">
         <v>7</v>
@@ -5023,7 +5050,7 @@
         <v>411</v>
       </c>
       <c r="B85" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C85">
         <v>7</v>
@@ -5043,7 +5070,7 @@
         <v>412</v>
       </c>
       <c r="B86" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C86">
         <v>7</v>
@@ -5063,7 +5090,7 @@
         <v>413</v>
       </c>
       <c r="B87" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C87">
         <v>7</v>
@@ -5083,7 +5110,7 @@
         <v>414</v>
       </c>
       <c r="B88" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C88">
         <v>7</v>
@@ -5103,7 +5130,7 @@
         <v>415</v>
       </c>
       <c r="B89" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C89">
         <v>7</v>
@@ -5123,7 +5150,7 @@
         <v>416</v>
       </c>
       <c r="B90" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -5143,7 +5170,7 @@
         <v>417</v>
       </c>
       <c r="B91" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -5163,7 +5190,7 @@
         <v>418</v>
       </c>
       <c r="B92" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -5183,7 +5210,7 @@
         <v>419</v>
       </c>
       <c r="B93" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -5203,7 +5230,7 @@
         <v>420</v>
       </c>
       <c r="B94" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -5223,7 +5250,7 @@
         <v>421</v>
       </c>
       <c r="B95" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C95">
         <v>7</v>
@@ -5243,7 +5270,7 @@
         <v>422</v>
       </c>
       <c r="B96" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -5263,7 +5290,7 @@
         <v>423</v>
       </c>
       <c r="B97" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -5283,7 +5310,7 @@
         <v>424</v>
       </c>
       <c r="B98" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -5303,7 +5330,7 @@
         <v>425</v>
       </c>
       <c r="B99" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -5323,7 +5350,7 @@
         <v>426</v>
       </c>
       <c r="B100" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -5343,7 +5370,7 @@
         <v>427</v>
       </c>
       <c r="B101" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C101">
         <v>7</v>
@@ -5363,7 +5390,7 @@
         <v>428</v>
       </c>
       <c r="B102" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -5383,7 +5410,7 @@
         <v>429</v>
       </c>
       <c r="B103" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C103">
         <v>7</v>
@@ -5403,7 +5430,7 @@
         <v>430</v>
       </c>
       <c r="B104" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -5423,7 +5450,7 @@
         <v>431</v>
       </c>
       <c r="B105" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C105">
         <v>7</v>
@@ -5443,7 +5470,7 @@
         <v>432</v>
       </c>
       <c r="B106" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -5463,7 +5490,7 @@
         <v>433</v>
       </c>
       <c r="B107" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -5483,7 +5510,7 @@
         <v>434</v>
       </c>
       <c r="B108" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C108">
         <v>7</v>
@@ -5503,7 +5530,7 @@
         <v>435</v>
       </c>
       <c r="B109" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -5523,7 +5550,7 @@
         <v>436</v>
       </c>
       <c r="B110" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -5543,7 +5570,7 @@
         <v>437</v>
       </c>
       <c r="B111" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -5563,7 +5590,7 @@
         <v>438</v>
       </c>
       <c r="B112" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -5583,7 +5610,7 @@
         <v>439</v>
       </c>
       <c r="B113" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -5603,7 +5630,7 @@
         <v>440</v>
       </c>
       <c r="B114" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -5623,7 +5650,7 @@
         <v>441</v>
       </c>
       <c r="B115" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -5643,7 +5670,7 @@
         <v>442</v>
       </c>
       <c r="B116" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -5663,7 +5690,7 @@
         <v>443</v>
       </c>
       <c r="B117" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -5683,7 +5710,7 @@
         <v>444</v>
       </c>
       <c r="B118" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -5703,7 +5730,7 @@
         <v>445</v>
       </c>
       <c r="B119" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -5723,7 +5750,7 @@
         <v>446</v>
       </c>
       <c r="B120" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -5743,7 +5770,7 @@
         <v>447</v>
       </c>
       <c r="B121" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -5763,7 +5790,7 @@
         <v>448</v>
       </c>
       <c r="B122" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -5783,7 +5810,7 @@
         <v>449</v>
       </c>
       <c r="B123" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -5803,7 +5830,7 @@
         <v>450</v>
       </c>
       <c r="B124" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -5823,7 +5850,7 @@
         <v>451</v>
       </c>
       <c r="B125" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -5843,7 +5870,7 @@
         <v>452</v>
       </c>
       <c r="B126" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -5863,7 +5890,7 @@
         <v>453</v>
       </c>
       <c r="B127" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -5883,7 +5910,7 @@
         <v>454</v>
       </c>
       <c r="B128" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C128">
         <v>7</v>
@@ -5903,7 +5930,7 @@
         <v>455</v>
       </c>
       <c r="B129" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -5923,7 +5950,7 @@
         <v>456</v>
       </c>
       <c r="B130" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -5943,7 +5970,7 @@
         <v>457</v>
       </c>
       <c r="B131" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -5963,7 +5990,7 @@
         <v>458</v>
       </c>
       <c r="B132" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -5983,7 +6010,7 @@
         <v>459</v>
       </c>
       <c r="B133" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -6003,7 +6030,7 @@
         <v>460</v>
       </c>
       <c r="B134" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C134">
         <v>7</v>
@@ -6023,7 +6050,7 @@
         <v>461</v>
       </c>
       <c r="B135" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -6043,7 +6070,7 @@
         <v>462</v>
       </c>
       <c r="B136" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C136">
         <v>7</v>
@@ -6063,7 +6090,7 @@
         <v>463</v>
       </c>
       <c r="B137" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -6083,7 +6110,7 @@
         <v>464</v>
       </c>
       <c r="B138" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C138">
         <v>7</v>
@@ -6103,7 +6130,7 @@
         <v>465</v>
       </c>
       <c r="B139" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -6123,7 +6150,7 @@
         <v>466</v>
       </c>
       <c r="B140" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -6143,7 +6170,7 @@
         <v>467</v>
       </c>
       <c r="B141" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -6163,7 +6190,7 @@
         <v>468</v>
       </c>
       <c r="B142" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C142">
         <v>7</v>
@@ -6183,7 +6210,7 @@
         <v>469</v>
       </c>
       <c r="B143" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -6203,7 +6230,7 @@
         <v>470</v>
       </c>
       <c r="B144" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -6223,7 +6250,7 @@
         <v>471</v>
       </c>
       <c r="B145" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -6243,7 +6270,7 @@
         <v>472</v>
       </c>
       <c r="B146" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C146">
         <v>7</v>
@@ -6263,7 +6290,7 @@
         <v>473</v>
       </c>
       <c r="B147" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C147">
         <v>7</v>
@@ -6283,7 +6310,7 @@
         <v>474</v>
       </c>
       <c r="B148" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -6303,7 +6330,7 @@
         <v>475</v>
       </c>
       <c r="B149" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C149">
         <v>7</v>
@@ -6323,7 +6350,7 @@
         <v>476</v>
       </c>
       <c r="B150" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -6343,7 +6370,7 @@
         <v>477</v>
       </c>
       <c r="B151" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C151">
         <v>7</v>
@@ -6363,7 +6390,7 @@
         <v>478</v>
       </c>
       <c r="B152" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C152">
         <v>7</v>
@@ -6383,7 +6410,7 @@
         <v>479</v>
       </c>
       <c r="B153" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C153">
         <v>7</v>
@@ -6403,7 +6430,7 @@
         <v>480</v>
       </c>
       <c r="B154" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C154">
         <v>7</v>
@@ -6423,7 +6450,7 @@
         <v>481</v>
       </c>
       <c r="B155" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -6443,7 +6470,7 @@
         <v>482</v>
       </c>
       <c r="B156" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C156">
         <v>7</v>
@@ -6463,7 +6490,7 @@
         <v>483</v>
       </c>
       <c r="B157" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C157">
         <v>7</v>
@@ -6483,7 +6510,7 @@
         <v>484</v>
       </c>
       <c r="B158" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C158">
         <v>7</v>
@@ -6503,7 +6530,7 @@
         <v>485</v>
       </c>
       <c r="B159" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C159">
         <v>7</v>
@@ -6523,7 +6550,7 @@
         <v>486</v>
       </c>
       <c r="B160" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C160">
         <v>7</v>
@@ -6543,7 +6570,7 @@
         <v>487</v>
       </c>
       <c r="B161" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C161">
         <v>7</v>
@@ -6563,7 +6590,7 @@
         <v>488</v>
       </c>
       <c r="B162" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C162">
         <v>7</v>
@@ -6583,7 +6610,7 @@
         <v>489</v>
       </c>
       <c r="B163" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C163">
         <v>7</v>
@@ -6603,7 +6630,7 @@
         <v>490</v>
       </c>
       <c r="B164" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C164">
         <v>7</v>
@@ -6623,7 +6650,7 @@
         <v>491</v>
       </c>
       <c r="B165" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C165">
         <v>7</v>
@@ -6643,7 +6670,7 @@
         <v>492</v>
       </c>
       <c r="B166" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C166">
         <v>7</v>
@@ -6663,7 +6690,7 @@
         <v>493</v>
       </c>
       <c r="B167" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C167">
         <v>7</v>
@@ -6683,7 +6710,7 @@
         <v>494</v>
       </c>
       <c r="B168" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C168">
         <v>7</v>
@@ -6703,7 +6730,7 @@
         <v>495</v>
       </c>
       <c r="B169" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C169">
         <v>7</v>
@@ -6723,7 +6750,7 @@
         <v>496</v>
       </c>
       <c r="B170" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C170">
         <v>7</v>
@@ -6743,7 +6770,7 @@
         <v>497</v>
       </c>
       <c r="B171" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C171">
         <v>7</v>
@@ -6763,7 +6790,7 @@
         <v>498</v>
       </c>
       <c r="B172" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C172">
         <v>7</v>
@@ -6783,7 +6810,7 @@
         <v>499</v>
       </c>
       <c r="B173" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C173">
         <v>7</v>
@@ -6803,7 +6830,7 @@
         <v>500</v>
       </c>
       <c r="B174" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C174">
         <v>7</v>
@@ -6823,7 +6850,7 @@
         <v>501</v>
       </c>
       <c r="B175" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C175">
         <v>7</v>
@@ -6843,7 +6870,7 @@
         <v>502</v>
       </c>
       <c r="B176" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6861,7 +6888,7 @@
         <v>503</v>
       </c>
       <c r="B177" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6879,7 +6906,7 @@
         <v>504</v>
       </c>
       <c r="B178" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6897,7 +6924,7 @@
         <v>505</v>
       </c>
       <c r="B179" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6915,7 +6942,7 @@
         <v>506</v>
       </c>
       <c r="B180" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C180">
         <v>7</v>
@@ -6943,7 +6970,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.85546875" bestFit="1" customWidth="1"/>
@@ -6965,7 +6992,7 @@
         <v>93</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D1" t="s">
         <v>92</v>
@@ -6980,627 +7007,654 @@
         <v>3</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>135</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>79</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2400</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>0</v>
+        <v>2880</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>113</v>
+        <v>136</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="E3" s="4">
-        <v>3000</v>
+        <v>240</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3000</v>
+        <v>288</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>112</v>
+        <v>138</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E4" s="4">
-        <v>2460</v>
+        <v>2400</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2460</v>
+        <v>2880</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>137</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E5" s="4">
-        <v>1051.2</v>
+        <v>240</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>1051.2</v>
+        <v>288</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E6" s="4">
-        <v>748.15</v>
+        <v>2450</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>748.15</v>
+        <v>2940</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="I6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E7" s="4">
-        <v>6096.65</v>
+        <v>240</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>6096.65</v>
+        <v>288</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="E8" s="4">
-        <v>7502.9</v>
+        <v>2200</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>7502.9</v>
+        <v>2640</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>132</v>
+      </c>
+      <c r="I8" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="4">
+        <v>240</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>288</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="4">
+        <v>748.15</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>748.15</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4">
+        <v>6096.65</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>6096.65</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4">
+        <v>7502.9</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>7502.9</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C13" t="s">
         <v>72</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D13" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E13" s="4">
         <f>16750</f>
         <v>16750</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="F13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>20100</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C14" t="s">
         <v>72</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D14" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E14" s="4">
         <f>887</f>
         <v>887</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="F14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>1064.3999999999999</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="H14" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" t="s">
         <v>72</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D15" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G15" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>0</v>
       </c>
-      <c r="H11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="H15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B16" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" t="s">
         <v>72</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D16" t="s">
+        <v>421</v>
+      </c>
+      <c r="E16" s="4">
+        <v>9205</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>11046</v>
+      </c>
+      <c r="H16" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="E17" s="4">
+        <v>5954</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>7144.8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="4">
+        <v>8026</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>9631.1999999999989</v>
+      </c>
+      <c r="H18" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>404</v>
+      </c>
+      <c r="E19" s="4">
+        <v>10932.1</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>13118.52</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="I19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="s">
+        <v>425</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>0</v>
       </c>
-      <c r="H12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="H20" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>406</v>
+      </c>
+      <c r="E21" s="4">
+        <v>320</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>320</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" t="s">
+        <v>406</v>
+      </c>
+      <c r="E22" s="4">
+        <v>640</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>640</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
+        <v>406</v>
+      </c>
+      <c r="E23" s="14">
+        <v>1800</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="14">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>1800</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C24" t="s">
         <v>55</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D24" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E24" s="4">
         <f>1140*12</f>
         <v>13680</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G24" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>13680</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="4">
-        <f>2836.8*12</f>
-        <v>34041.600000000006</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>34041.600000000006</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="4">
-        <f>1518*12</f>
-        <v>18216</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>18216</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I15" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="4">
-        <v>516</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>516</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="4">
-        <v>456</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>456</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="135" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="4">
-        <v>660</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>660</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>190</v>
-      </c>
-      <c r="E19" s="4">
-        <v>434.5</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>434.5</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="4">
-        <v>2400</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2880</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="4">
-        <v>2400</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2880</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I21" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="4">
-        <v>2450</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2940</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I22" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="4">
-        <v>2200</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2640</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="4">
-        <v>160</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -7608,7 +7662,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>55</v>
@@ -7617,18 +7671,18 @@
         <v>108</v>
       </c>
       <c r="E25" s="4">
-        <f>2400*12</f>
-        <v>28800</v>
+        <f>2836.8*12</f>
+        <v>34041.600000000006</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G25" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>28800</v>
+        <v>34041.600000000006</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -7636,248 +7690,279 @@
         <v>12</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
         <v>55</v>
       </c>
       <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="4">
+        <f>1518*12</f>
+        <v>18216</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>18216</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E27" s="4">
+        <f>2400*12</f>
+        <v>28800</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>28800</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="4">
         <f>1320*12</f>
         <v>15840</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G28" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>15840</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="4">
-        <v>3198.13</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3198.13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="4">
-        <v>3322.8</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3322.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="E29" s="4">
-        <v>3138.27</v>
+        <v>516</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G29" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3138.27</v>
+        <v>516</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="I29" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E30" s="4">
-        <v>240</v>
+        <v>456</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
+        <v>456</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="E31" s="4">
-        <v>240</v>
+        <v>660</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
+        <v>660</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="E32" s="4">
-        <v>240</v>
+        <v>434.5</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
+        <v>434.5</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>13</v>
+      <c r="A33" t="s">
+        <v>410</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
+        <v>413</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="E33" s="4">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4">
+        <v>2</v>
+      </c>
+      <c r="G33" s="14">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>133</v>
+        <v>412</v>
+      </c>
+      <c r="I33" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>171</v>
+        <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>170</v>
-      </c>
-      <c r="E34" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1051.2</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>10000</v>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="2"/>
+        <v>1051.2</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D35" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E35" s="5">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G35" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="2"/>
@@ -7887,23 +7972,23 @@
         <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D36" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E36" s="5">
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G36" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="2"/>
@@ -7913,182 +7998,206 @@
         <v>98</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>168</v>
       </c>
       <c r="E37" s="5">
-        <v>16800</v>
+        <v>15000</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G37" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>15000</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="5">
         <v>16800</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="F38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="5">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>16800</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" t="s">
-        <v>406</v>
-      </c>
-      <c r="E38" s="4">
-        <v>10932.1</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>13118.52</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="I38" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="I38" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>414</v>
+        <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C39" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>409</v>
-      </c>
-      <c r="E39" s="4">
-        <v>320</v>
+        <v>24</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G39" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>320</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>414</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C40" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="D40" t="s">
-        <v>409</v>
+        <v>10</v>
       </c>
       <c r="E40" s="4">
-        <v>640</v>
+        <v>3000</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>640</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>414</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>409</v>
-      </c>
-      <c r="E41" s="14">
-        <v>1800</v>
+        <v>11</v>
+      </c>
+      <c r="E41" s="4">
+        <v>2460</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>1800</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>413</v>
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>406</v>
+        <v>26</v>
       </c>
       <c r="E42" s="4">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="I42" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="C43"/>
-      <c r="G43" s="13"/>
-      <c r="I43" s="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="4">
+        <v>3198.13</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="13">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>3198.13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="4">
+        <v>3322.8</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="15">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>3322.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="4">
+        <v>3138.27</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="15">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>3138.27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="C46"/>
+      <c r="G46" s="13"/>
+      <c r="I46" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8102,7 +8211,7 @@
           <x14:formula1>
             <xm:f>Provisions!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>C45:C1048576 C1:C43</xm:sqref>
+          <xm:sqref>C48:C1048576 C1:C46</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8126,21 +8235,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B2">
         <f>5735*2.5</f>
@@ -8183,39 +8292,39 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" t="s">
+        <v>401</v>
+      </c>
+      <c r="J1" t="s">
         <v>398</v>
-      </c>
-      <c r="G1" t="s">
-        <v>186</v>
-      </c>
-      <c r="H1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I1" t="s">
-        <v>403</v>
-      </c>
-      <c r="J1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>70</v>
@@ -8225,7 +8334,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E2" s="1">
         <f>310*1.2</f>
@@ -8238,7 +8347,7 @@
         <v>120</v>
       </c>
       <c r="H2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I2">
         <v>37</v>
@@ -8249,7 +8358,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -8258,7 +8367,7 @@
         <v>0.12559999999999999</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E3" s="1">
         <v>0.12559999999999999</v>
@@ -8270,7 +8379,7 @@
         <v>140</v>
       </c>
       <c r="H3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I3">
         <f>12</f>
